--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -9298,9 +9298,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J66" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J66" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K66" s="33" t="inlineStr">
@@ -9332,7 +9332,7 @@
       <c r="Q66" s="24" t="n"/>
       <c r="R66" s="24" t="inlineStr">
         <is>
-          <t>Aggregate counts only; no per-child history</t>
+          <t>Attendance tab: months, percent and days away</t>
         </is>
       </c>
       <c r="S66" s="24" t="n"/>
@@ -9506,9 +9506,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J68" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K68" s="33" t="inlineStr">
@@ -9540,7 +9540,7 @@
       <c r="Q68" s="24" t="n"/>
       <c r="R68" s="24" t="inlineStr">
         <is>
-          <t>Cannot scope the fee list to one child</t>
+          <t>Fees tab scoped to the child</t>
         </is>
       </c>
       <c r="S68" s="24" t="n"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>/school/fees</t>
+          <t>/school/students/[id]</t>
         </is>
       </c>
     </row>
@@ -9610,9 +9610,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J69" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K69" s="33" t="inlineStr">
@@ -9644,7 +9644,7 @@
       <c r="Q69" s="24" t="n"/>
       <c r="R69" s="24" t="inlineStr">
         <is>
-          <t>No per-student document view</t>
+          <t>Documents tab with download</t>
         </is>
       </c>
       <c r="S69" s="24" t="n"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>/school/documents</t>
+          <t>/school/students/[id]</t>
         </is>
       </c>
     </row>
@@ -9714,9 +9714,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J70" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K70" s="33" t="inlineStr">
@@ -9748,7 +9748,7 @@
       <c r="Q70" s="24" t="n"/>
       <c r="R70" s="24" t="inlineStr">
         <is>
-          <t>Discipline list filters status, not student</t>
+          <t>Conduct tab: incidents for this child</t>
         </is>
       </c>
       <c r="S70" s="24" t="n"/>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>/school/discipline</t>
+          <t>/school/students/[id]</t>
         </is>
       </c>
     </row>
@@ -10026,9 +10026,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J73" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
@@ -10060,7 +10060,7 @@
       <c r="Q73" s="24" t="n"/>
       <c r="R73" s="24" t="inlineStr">
         <is>
-          <t>Circulation desk, not a per-student view</t>
+          <t>Library tab: loans, overdue and fines</t>
         </is>
       </c>
       <c r="S73" s="24" t="n"/>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>/school/library</t>
+          <t>/school/students/[id]</t>
         </is>
       </c>
     </row>
@@ -18450,9 +18450,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J154" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J154" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K154" s="33" t="inlineStr">
@@ -18484,7 +18484,7 @@
       <c r="Q154" s="24" t="n"/>
       <c r="R154" s="24" t="inlineStr">
         <is>
-          <t>Verify endpoint has no caller in the frontend</t>
+          <t>Sign off a paper; refuses whoever entered the marks</t>
         </is>
       </c>
       <c r="S154" s="24" t="n"/>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/exams</t>
         </is>
       </c>
     </row>
@@ -23962,14 +23962,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J207" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K207" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J207" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K207" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L207" s="24" t="inlineStr">
@@ -23996,7 +23996,7 @@
       <c r="Q207" s="24" t="n"/>
       <c r="R207" s="24" t="inlineStr">
         <is>
-          <t>No members screen; borrowers only a picker</t>
+          <t>Who holds what, with limit and can-borrow</t>
         </is>
       </c>
       <c r="S207" s="24" t="n"/>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/library/members</t>
         </is>
       </c>
     </row>
@@ -26770,9 +26770,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J234" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J234" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K234" s="33" t="inlineStr">
@@ -26804,7 +26804,7 @@
       <c r="Q234" s="24" t="n"/>
       <c r="R234" s="24" t="inlineStr">
         <is>
-          <t>Host-decision endpoint has no screen</t>
+          <t>Host confirms or declines an expected visitor</t>
         </is>
       </c>
       <c r="S234" s="24" t="n"/>
@@ -28018,9 +28018,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J246" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J246" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K246" s="33" t="inlineStr">
@@ -28052,7 +28052,7 @@
       <c r="Q246" s="24" t="n"/>
       <c r="R246" s="24" t="inlineStr">
         <is>
-          <t>Per asset only; assignments register unused</t>
+          <t>Assignments tab: what is out and with whom</t>
         </is>
       </c>
       <c r="S246" s="24" t="n"/>
@@ -33119,9 +33119,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="K295" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="K295" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L295" s="24" t="inlineStr">
@@ -33148,7 +33148,7 @@
       <c r="Q295" s="24" t="n"/>
       <c r="R295" s="24" t="inlineStr">
         <is>
-          <t>Settings hub endpoint unused</t>
+          <t>Settings index with set-up state</t>
         </is>
       </c>
       <c r="S295" s="24" t="n"/>
@@ -33180,7 +33180,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>/school/profile</t>
+          <t>/school/settings</t>
         </is>
       </c>
     </row>
@@ -33426,14 +33426,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J298" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K298" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J298" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K298" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L298" s="24" t="inlineStr">
@@ -33460,7 +33460,7 @@
       <c r="Q298" s="24" t="n"/>
       <c r="R298" s="24" t="inlineStr">
         <is>
-          <t>Razorpay keys only; integrations endpoint unused</t>
+          <t>Outside services and whether they are connected</t>
         </is>
       </c>
       <c r="S298" s="24" t="n"/>
@@ -33492,7 +33492,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>/school/fees/online</t>
+          <t>/school/settings</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -30514,14 +30514,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J270" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K270" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J270" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K270" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L270" s="24" t="inlineStr">
@@ -30548,7 +30548,7 @@
       <c r="Q270" s="24" t="n"/>
       <c r="R270" s="24" t="inlineStr">
         <is>
-          <t>Counts only; no trends or charts</t>
+          <t>Headline tiles plus attendance and money trends, and the index of every report</t>
         </is>
       </c>
       <c r="S270" s="24" t="n"/>
@@ -30580,7 +30580,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>/school</t>
+          <t>/school/reports</t>
         </is>
       </c>
     </row>
@@ -30618,9 +30618,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J271" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J271" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K271" s="33" t="inlineStr">
@@ -30652,7 +30652,7 @@
       <c r="Q271" s="24" t="n"/>
       <c r="R271" s="24" t="inlineStr">
         <is>
-          <t>Stage counts inline; funnel endpoint unused</t>
+          <t>Funnel by stage with conversion rate</t>
         </is>
       </c>
       <c r="S271" s="24" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>/school/admissions</t>
+          <t>/school/reports/admissions</t>
         </is>
       </c>
     </row>
@@ -30722,14 +30722,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J272" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K272" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J272" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K272" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L272" s="24" t="inlineStr">
@@ -30756,7 +30756,7 @@
       <c r="Q272" s="24" t="n"/>
       <c r="R272" s="24" t="inlineStr">
         <is>
-          <t>No class strength or year-on-year table</t>
+          <t>Class, section and capacity, with year on year</t>
         </is>
       </c>
       <c r="S272" s="24" t="n"/>
@@ -30788,7 +30788,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>/school/students</t>
+          <t>/school/reports/strength</t>
         </is>
       </c>
     </row>
@@ -30826,14 +30826,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J273" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K273" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J273" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K273" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L273" s="24" t="inlineStr">
@@ -30860,7 +30860,7 @@
       <c r="Q273" s="24" t="n"/>
       <c r="R273" s="24" t="inlineStr">
         <is>
-          <t>No demographic breakdown anywhere</t>
+          <t>Gender, age and blood group, with how much is on file</t>
         </is>
       </c>
       <c r="S273" s="24" t="n"/>
@@ -30892,7 +30892,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/reports/demographics</t>
         </is>
       </c>
     </row>
@@ -31034,14 +31034,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J275" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K275" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J275" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K275" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L275" s="24" t="inlineStr">
@@ -31068,7 +31068,7 @@
       <c r="Q275" s="24" t="n"/>
       <c r="R275" s="24" t="inlineStr">
         <is>
-          <t>One section at a time; no threshold list</t>
+          <t>School-wide, with an adjustable threshold and CSV</t>
         </is>
       </c>
       <c r="S275" s="24" t="n"/>
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>/school/reports/attendance</t>
+          <t>/school/reports/chronic-absence</t>
         </is>
       </c>
     </row>
@@ -31138,14 +31138,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J276" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K276" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J276" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K276" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L276" s="24" t="inlineStr">
@@ -31172,7 +31172,7 @@
       <c r="Q276" s="24" t="n"/>
       <c r="R276" s="24" t="inlineStr">
         <is>
-          <t>Per-section results; no cohort analysis</t>
+          <t>Whole-cohort analysis per exam</t>
         </is>
       </c>
       <c r="S276" s="24" t="n"/>
@@ -31204,7 +31204,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>/school/report-cards</t>
+          <t>/school/reports/exams</t>
         </is>
       </c>
     </row>
@@ -31242,14 +31242,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J277" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K277" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J277" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K277" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L277" s="24" t="inlineStr">
@@ -31276,7 +31276,7 @@
       <c r="Q277" s="24" t="n"/>
       <c r="R277" s="24" t="inlineStr">
         <is>
-          <t>No subject performance screen or endpoint</t>
+          <t>Pass rate and average per subject, weakest first (in a tab, complete)</t>
         </is>
       </c>
       <c r="S277" s="24" t="n"/>
@@ -31308,7 +31308,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/reports/exams</t>
         </is>
       </c>
     </row>
@@ -31346,14 +31346,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J278" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K278" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J278" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K278" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L278" s="24" t="inlineStr">
@@ -31380,7 +31380,7 @@
       <c r="Q278" s="24" t="n"/>
       <c r="R278" s="24" t="inlineStr">
         <is>
-          <t>No pass rate or grade distribution</t>
+          <t>Pass rate tile and grade ring (in a tab, complete)</t>
         </is>
       </c>
       <c r="S278" s="24" t="n"/>
@@ -31412,7 +31412,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>/school/report-cards</t>
+          <t>/school/reports/exams</t>
         </is>
       </c>
     </row>
@@ -31450,9 +31450,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J279" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J279" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K279" s="33" t="inlineStr">
@@ -31484,7 +31484,7 @@
       <c r="Q279" s="24" t="n"/>
       <c r="R279" s="24" t="inlineStr">
         <is>
-          <t>Receipts list; no head-wise rollup</t>
+          <t>By head, class, mode and month, with CSV</t>
         </is>
       </c>
       <c r="S279" s="24" t="n"/>
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>/school/accounts</t>
+          <t>/school/reports/fee-collection</t>
         </is>
       </c>
     </row>
@@ -31554,9 +31554,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J280" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J280" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K280" s="33" t="inlineStr">
@@ -31588,7 +31588,7 @@
       <c r="Q280" s="24" t="n"/>
       <c r="R280" s="24" t="inlineStr">
         <is>
-          <t>Filtered rows; no ageing or defaulters</t>
+          <t>Five ageing buckets and the defaulter list, with CSV</t>
         </is>
       </c>
       <c r="S280" s="24" t="n"/>
@@ -31620,7 +31620,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>/school/fees</t>
+          <t>/school/reports/dues</t>
         </is>
       </c>
     </row>
@@ -31762,14 +31762,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J282" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K282" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J282" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K282" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L282" s="24" t="inlineStr">
@@ -31796,7 +31796,7 @@
       <c r="Q282" s="24" t="n"/>
       <c r="R282" s="24" t="inlineStr">
         <is>
-          <t>Single day; no monthly totals</t>
+          <t>A month per person, holidays excluded</t>
         </is>
       </c>
       <c r="S282" s="24" t="n"/>
@@ -31828,7 +31828,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>/school/staff-attendance</t>
+          <t>/school/reports/staff-attendance</t>
         </is>
       </c>
     </row>
@@ -31970,14 +31970,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J284" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K284" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J284" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K284" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L284" s="24" t="inlineStr">
@@ -32004,7 +32004,7 @@
       <c r="Q284" s="24" t="n"/>
       <c r="R284" s="24" t="inlineStr">
         <is>
-          <t>No teacher performance screen or endpoint</t>
+          <t>Counts of work done, stated as not a ranking</t>
         </is>
       </c>
       <c r="S284" s="24" t="n"/>
@@ -32036,7 +32036,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/reports/teachers</t>
         </is>
       </c>
     </row>
@@ -32074,14 +32074,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J285" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K285" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J285" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K285" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L285" s="24" t="inlineStr">
@@ -32108,7 +32108,7 @@
       <c r="Q285" s="24" t="n"/>
       <c r="R285" s="24" t="inlineStr">
         <is>
-          <t>Tiles only; no utilisation report</t>
+          <t>Riders against seats, over-capacity routes flagged</t>
         </is>
       </c>
       <c r="S285" s="24" t="n"/>
@@ -32140,7 +32140,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>/school/transport</t>
+          <t>/school/reports/transport</t>
         </is>
       </c>
     </row>
@@ -32178,14 +32178,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J286" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K286" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J286" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K286" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L286" s="24" t="inlineStr">
@@ -32212,7 +32212,7 @@
       <c r="Q286" s="24" t="n"/>
       <c r="R286" s="24" t="inlineStr">
         <is>
-          <t>Counts only; no period usage report</t>
+          <t>Issues and returns by month, and top titles</t>
         </is>
       </c>
       <c r="S286" s="24" t="n"/>
@@ -32244,7 +32244,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>/school/library</t>
+          <t>/school/reports/library</t>
         </is>
       </c>
     </row>
@@ -32282,14 +32282,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J287" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K287" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J287" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K287" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L287" s="24" t="inlineStr">
@@ -32316,7 +32316,7 @@
       <c r="Q287" s="24" t="n"/>
       <c r="R287" s="24" t="inlineStr">
         <is>
-          <t>Tiles only; no valuation report</t>
+          <t>Stock and asset value by category, and low stock</t>
         </is>
       </c>
       <c r="S287" s="24" t="n"/>
@@ -32348,7 +32348,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/reports/inventory</t>
         </is>
       </c>
     </row>
@@ -32386,14 +32386,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J288" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K288" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J288" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K288" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L288" s="24" t="inlineStr">
@@ -32420,7 +32420,7 @@
       <c r="Q288" s="24" t="n"/>
       <c r="R288" s="24" t="inlineStr">
         <is>
-          <t>Per-notice counts; no aggregate report</t>
+          <t>By audience, month and channel, skipped kept apart from failed</t>
         </is>
       </c>
       <c r="S288" s="24" t="n"/>
@@ -32452,7 +32452,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>/school/notices</t>
+          <t>/school/reports/notifications</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -17410,14 +17410,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J144" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K144" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J144" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K144" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L144" s="24" t="inlineStr">
@@ -17444,7 +17444,7 @@
       <c r="Q144" s="24" t="n"/>
       <c r="R144" s="24" t="inlineStr">
         <is>
-          <t>Paper counts only; no exam dashboard</t>
+          <t>Readiness checklist per paper, with what blocks publication</t>
         </is>
       </c>
       <c r="S144" s="24" t="n"/>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>/school/exams</t>
+          <t>/school/exams/[id]</t>
         </is>
       </c>
     </row>
@@ -17722,14 +17722,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J147" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K147" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J147" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K147" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L147" s="24" t="inlineStr">
@@ -17756,7 +17756,7 @@
       <c r="Q147" s="24" t="n"/>
       <c r="R147" s="24" t="inlineStr">
         <is>
-          <t>Per-paper date only; no datesheet screen</t>
+          <t>Papers by day, with per-class clash detection</t>
         </is>
       </c>
       <c r="S147" s="24" t="n"/>
@@ -17788,7 +17788,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>/school/exams</t>
+          <t>/school/exams/[id]/datesheet</t>
         </is>
       </c>
     </row>
@@ -17826,14 +17826,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J148" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K148" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J148" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K148" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L148" s="24" t="inlineStr">
@@ -17860,7 +17860,7 @@
       <c r="Q148" s="24" t="n"/>
       <c r="R148" s="24" t="inlineStr">
         <is>
-          <t>No exam hall or seat allocation anywhere</t>
+          <t>Room allocation, fills in order, move a child</t>
         </is>
       </c>
       <c r="S148" s="24" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/exams/[id]/halls</t>
         </is>
       </c>
     </row>
@@ -17930,14 +17930,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J149" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K149" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J149" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K149" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L149" s="24" t="inlineStr">
@@ -17964,7 +17964,7 @@
       <c r="Q149" s="24" t="n"/>
       <c r="R149" s="24" t="inlineStr">
         <is>
-          <t>No invigilation assignment anywhere</t>
+          <t>Per-room duty with double-booking refused, plus roster</t>
         </is>
       </c>
       <c r="S149" s="24" t="n"/>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/exams/[id]/invigilation</t>
         </is>
       </c>
     </row>
@@ -18034,14 +18034,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J150" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K150" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J150" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K150" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L150" s="24" t="inlineStr">
@@ -18068,7 +18068,7 @@
       <c r="Q150" s="24" t="n"/>
       <c r="R150" s="24" t="inlineStr">
         <is>
-          <t>No admit card UI or endpoint</t>
+          <t>Per class, with room per paper, prints as PDF</t>
         </is>
       </c>
       <c r="S150" s="24" t="n"/>
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/exams/[id]/admit-cards</t>
         </is>
       </c>
     </row>
@@ -18242,14 +18242,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J152" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K152" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J152" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K152" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L152" s="24" t="inlineStr">
@@ -18276,7 +18276,7 @@
       <c r="Q152" s="24" t="n"/>
       <c r="R152" s="24" t="inlineStr">
         <is>
-          <t>One max mark per paper; no internal split</t>
+          <t>Parts must add up; the total is their sum</t>
         </is>
       </c>
       <c r="S152" s="24" t="n"/>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/exams/papers/[paperId]/components</t>
         </is>
       </c>
     </row>
@@ -18346,9 +18346,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J153" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J153" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K153" s="33" t="inlineStr">
@@ -18380,7 +18380,7 @@
       <c r="Q153" s="24" t="n"/>
       <c r="R153" s="24" t="inlineStr">
         <is>
-          <t>Marks import exists but admin-only</t>
+          <t>Teacher uploads for their own paper, checked before written</t>
         </is>
       </c>
       <c r="S153" s="24" t="n"/>
@@ -18412,7 +18412,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>/school/data-desk</t>
+          <t>/teacher/marks/papers/[id]/import</t>
         </is>
       </c>
     </row>
@@ -18658,9 +18658,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J156" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J156" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K156" s="33" t="inlineStr">
@@ -18692,7 +18692,7 @@
       <c r="Q156" s="24" t="n"/>
       <c r="R156" s="24" t="inlineStr">
         <is>
-          <t>Publish is admin-only; principal approves</t>
+          <t>Principal publishes, told what is outstanding first</t>
         </is>
       </c>
       <c r="S156" s="24" t="n"/>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>/school/exams</t>
+          <t>/principal/exams</t>
         </is>
       </c>
     </row>
@@ -18970,14 +18970,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J159" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K159" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J159" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K159" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L159" s="24" t="inlineStr">
@@ -19004,7 +19004,7 @@
       <c r="Q159" s="24" t="n"/>
       <c r="R159" s="24" t="inlineStr">
         <is>
-          <t>Section move, not a result-driven decision</t>
+          <t>Result-driven suggestion, review kept apart from fail</t>
         </is>
       </c>
       <c r="S159" s="24" t="n"/>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>/school/students</t>
+          <t>/school/exams/[id]/promotion</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -6802,14 +6802,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J42" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K42" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J42" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K42" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L42" s="24" t="inlineStr">
@@ -6836,7 +6836,7 @@
       <c r="Q42" s="24" t="n"/>
       <c r="R42" s="24" t="inlineStr">
         <is>
-          <t>Deliberate: no student login; parent portal stands in</t>
+          <t>Homework due, today's lessons, attendance, notices</t>
         </is>
       </c>
       <c r="S42" s="24" t="n"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/student</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16716,7 @@
       <c r="Q137" s="24" t="n"/>
       <c r="R137" s="24" t="inlineStr">
         <is>
-          <t>Parent acts; no student login exists</t>
+          <t>The child sees their own homework, not via a parent</t>
         </is>
       </c>
       <c r="S137" s="24" t="n"/>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>/parent/children/[id]/homework</t>
+          <t>/student/homework</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16820,7 @@
       <c r="Q138" s="24" t="n"/>
       <c r="R138" s="24" t="inlineStr">
         <is>
-          <t>Submit or edit with comment and file</t>
+          <t>The child hands work in themselves; the record says who did</t>
         </is>
       </c>
       <c r="S138" s="24" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>/parent/children/[id]/homework</t>
+          <t>/student/homework</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17236,7 @@
       <c r="Q142" s="24" t="n"/>
       <c r="R142" s="24" t="inlineStr">
         <is>
-          <t>Progress with status, file and note</t>
+          <t>Submission with teacher remark and review state</t>
         </is>
       </c>
       <c r="S142" s="24" t="n"/>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>/parent/children/[id]/projects</t>
+          <t>/student/homework</t>
         </is>
       </c>
     </row>
@@ -18762,9 +18762,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J157" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J157" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K157" s="33" t="inlineStr">
@@ -18796,7 +18796,7 @@
       <c r="Q157" s="24" t="n"/>
       <c r="R157" s="24" t="inlineStr">
         <is>
-          <t>Full result, but parent login only</t>
+          <t>Published only, withheld stays withheld</t>
         </is>
       </c>
       <c r="S157" s="24" t="n"/>
@@ -18828,7 +18828,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>/parent/children/[id]/exams/[examId]</t>
+          <t>/student/exams/[examId]</t>
         </is>
       </c>
     </row>
@@ -18866,9 +18866,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J158" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J158" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K158" s="33" t="inlineStr">
@@ -18900,7 +18900,7 @@
       <c r="Q158" s="24" t="n"/>
       <c r="R158" s="24" t="inlineStr">
         <is>
-          <t>Report card PDF; no student login</t>
+          <t>Same renderer as the school and the parents</t>
         </is>
       </c>
       <c r="S158" s="24" t="n"/>
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>/school/report-cards</t>
+          <t>/student/exams/[examId]</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -3258,9 +3258,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J8" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J8" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K8" s="34" t="inlineStr">
@@ -3292,7 +3292,7 @@
       <c r="Q8" s="24" t="n"/>
       <c r="R8" s="24" t="inlineStr">
         <is>
-          <t>Role buttons on landing, no workspace chooser</t>
+          <t>Every portal, with a line on picking the right one</t>
         </is>
       </c>
       <c r="S8" s="24" t="n"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="V8" s="24" t="inlineStr">
         <is>
-          <t>Role buttons on landing, no workspace chooser</t>
+          <t>Every portal, with a line on picking the right one</t>
         </is>
       </c>
       <c r="W8" s="15">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/workspace</t>
         </is>
       </c>
     </row>
@@ -3470,14 +3470,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J10" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K10" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L10" s="24" t="inlineStr">
@@ -3504,7 +3504,7 @@
       <c r="Q10" s="24" t="n"/>
       <c r="R10" s="24" t="inlineStr">
         <is>
-          <t>No forgot-password UI or endpoint anywhere</t>
+          <t>Same answer whether the account exists or not</t>
         </is>
       </c>
       <c r="S10" s="24" t="n"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/account/forgot-password</t>
         </is>
       </c>
     </row>
@@ -3574,14 +3574,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J11" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K11" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K11" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L11" s="24" t="inlineStr">
@@ -3608,7 +3608,7 @@
       <c r="Q11" s="24" t="n"/>
       <c r="R11" s="24" t="inlineStr">
         <is>
-          <t>Only an admin-issued temporary password</t>
+          <t>Code dies on use, on reissue and after five guesses</t>
         </is>
       </c>
       <c r="S11" s="24" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/account/reset-password</t>
         </is>
       </c>
     </row>
@@ -3782,14 +3782,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J13" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K13" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K13" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
@@ -3816,7 +3816,7 @@
       <c r="Q13" s="24" t="n"/>
       <c r="R13" s="24" t="inlineStr">
         <is>
-          <t>Missing for admin, principal, accountant, parent</t>
+          <t>Every guard forces it when somebody else set the password</t>
         </is>
       </c>
       <c r="S13" s="24" t="n"/>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>/teacher/change-password</t>
+          <t>/account/change-password</t>
         </is>
       </c>
     </row>
@@ -3886,9 +3886,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J14" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J14" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="34" t="inlineStr">
@@ -3920,7 +3920,7 @@
       <c r="Q14" s="24" t="n"/>
       <c r="R14" s="24" t="inlineStr">
         <is>
-          <t>Guards redirect on 401; no screen</t>
+          <t>Expired and forbidden, and the 401 interceptor routes here</t>
         </is>
       </c>
       <c r="S14" s="24" t="n"/>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="V14" s="24" t="inlineStr">
         <is>
-          <t>Guards redirect on 401; no screen</t>
+          <t>Expired and forbidden, and the 401 interceptor routes here</t>
         </is>
       </c>
       <c r="W14" s="15">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/account/denied</t>
         </is>
       </c>
     </row>
@@ -7010,14 +7010,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J44" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K44" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J44" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K44" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L44" s="24" t="inlineStr">
@@ -7044,7 +7044,7 @@
       <c r="Q44" s="24" t="n"/>
       <c r="R44" s="24" t="inlineStr">
         <is>
-          <t>Forty-line stub with one link</t>
+          <t>Collected today and this month against what is owed</t>
         </is>
       </c>
       <c r="S44" s="24" t="n"/>
@@ -7114,14 +7114,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J45" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K45" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J45" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K45" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L45" s="24" t="inlineStr">
@@ -7148,7 +7148,7 @@
       <c r="Q45" s="24" t="n"/>
       <c r="R45" s="24" t="inlineStr">
         <is>
-          <t>No HR portal; pipeline endpoint unused</t>
+          <t>Staff and leave panel, shown to whoever holds hr.manage</t>
         </is>
       </c>
       <c r="S45" s="24" t="n"/>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/staff</t>
         </is>
       </c>
     </row>
@@ -7218,9 +7218,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J46" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J46" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K46" s="33" t="inlineStr">
@@ -7252,7 +7252,7 @@
       <c r="Q46" s="24" t="n"/>
       <c r="R46" s="24" t="inlineStr">
         <is>
-          <t>Pipeline exists, no officer portal</t>
+          <t>Admissions panel, shown to whoever holds admissions.manage</t>
         </is>
       </c>
       <c r="S46" s="24" t="n"/>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>/school/admissions</t>
+          <t>/staff</t>
         </is>
       </c>
     </row>
@@ -7322,9 +7322,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J47" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J47" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K47" s="33" t="inlineStr">
@@ -7356,7 +7356,7 @@
       <c r="Q47" s="24" t="n"/>
       <c r="R47" s="24" t="inlineStr">
         <is>
-          <t>Real dashboard, school-admin only</t>
+          <t>Transport panel, shown to whoever holds transport.manage</t>
         </is>
       </c>
       <c r="S47" s="24" t="n"/>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>/school/transport</t>
+          <t>/staff</t>
         </is>
       </c>
     </row>
@@ -7426,9 +7426,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J48" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J48" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K48" s="33" t="inlineStr">
@@ -7460,7 +7460,7 @@
       <c r="Q48" s="24" t="n"/>
       <c r="R48" s="24" t="inlineStr">
         <is>
-          <t>Library dashboard is school-admin only</t>
+          <t>Library panel, shown to whoever holds library.manage</t>
         </is>
       </c>
       <c r="S48" s="24" t="n"/>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>/school/library</t>
+          <t>/staff</t>
         </is>
       </c>
     </row>
@@ -22610,9 +22610,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J194" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J194" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K194" s="33" t="inlineStr">
@@ -22644,7 +22644,7 @@
       <c r="Q194" s="24" t="n"/>
       <c r="R194" s="24" t="inlineStr">
         <is>
-          <t>No vehicle detail page; endpoint unused</t>
+          <t>Expiries flagged, fuel and service log</t>
         </is>
       </c>
       <c r="S194" s="24" t="n"/>
@@ -22676,7 +22676,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>/school/transport/vehicles</t>
+          <t>/school/transport/vehicles/[id]</t>
         </is>
       </c>
     </row>
@@ -22922,14 +22922,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J197" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K197" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J197" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K197" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L197" s="24" t="inlineStr">
@@ -22956,7 +22956,7 @@
       <c r="Q197" s="24" t="n"/>
       <c r="R197" s="24" t="inlineStr">
         <is>
-          <t>Stops only inside the route modal</t>
+          <t>Stops in order with times, and the riders</t>
         </is>
       </c>
       <c r="S197" s="24" t="n"/>
@@ -22988,7 +22988,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>/school/transport/routes</t>
+          <t>/school/transport/routes/[id]</t>
         </is>
       </c>
     </row>
@@ -23338,9 +23338,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J201" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J201" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K201" s="33" t="inlineStr">
@@ -23372,7 +23372,7 @@
       <c r="Q201" s="24" t="n"/>
       <c r="R201" s="24" t="inlineStr">
         <is>
-          <t>Last-seen link only; no live map</t>
+          <t>Last reported position, staleness stated</t>
         </is>
       </c>
       <c r="S201" s="24" t="n"/>
@@ -23404,7 +23404,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>/school/transport/vehicles</t>
+          <t>/school/transport/live</t>
         </is>
       </c>
     </row>
@@ -23546,9 +23546,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J203" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J203" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K203" s="33" t="inlineStr">
@@ -23580,7 +23580,7 @@
       <c r="Q203" s="24" t="n"/>
       <c r="R203" s="24" t="inlineStr">
         <is>
-          <t>Fuel and service log in a modal</t>
+          <t>Fuel and service entries with odometer</t>
         </is>
       </c>
       <c r="S203" s="24" t="n"/>
@@ -23612,7 +23612,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>/school/transport/vehicles</t>
+          <t>/school/transport/vehicles/[id]</t>
         </is>
       </c>
     </row>
@@ -29786,9 +29786,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J263" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J263" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K263" s="33" t="inlineStr">
@@ -29820,7 +29820,7 @@
       <c r="Q263" s="24" t="n"/>
       <c r="R263" s="24" t="inlineStr">
         <is>
-          <t>A filter, not a student documents view</t>
+          <t>Expiring and unverified visible at a glance</t>
         </is>
       </c>
       <c r="S263" s="24" t="n"/>
@@ -29852,7 +29852,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>/school/documents</t>
+          <t>/school/documents/students</t>
         </is>
       </c>
     </row>
@@ -29890,9 +29890,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J264" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J264" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K264" s="33" t="inlineStr">
@@ -29924,7 +29924,7 @@
       <c r="Q264" s="24" t="n"/>
       <c r="R264" s="24" t="inlineStr">
         <is>
-          <t>Same repository filtered for staff</t>
+          <t>Same view, filtered to staff</t>
         </is>
       </c>
       <c r="S264" s="24" t="n"/>
@@ -29956,7 +29956,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>/school/documents</t>
+          <t>/school/documents/staff</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -7530,9 +7530,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J49" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J49" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K49" s="33" t="inlineStr">
@@ -7564,7 +7564,7 @@
       <c r="Q49" s="24" t="n"/>
       <c r="R49" s="24" t="inlineStr">
         <is>
-          <t>Stat cards atop the list; no dashboard page</t>
+          <t>Funnel, plus what is waiting on us</t>
         </is>
       </c>
       <c r="S49" s="24" t="n"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>/school/admissions</t>
+          <t>/school/admissions/dashboard</t>
         </is>
       </c>
     </row>
@@ -7946,14 +7946,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J53" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K53" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J53" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K53" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L53" s="24" t="inlineStr">
@@ -7980,7 +7980,7 @@
       <c r="Q53" s="24" t="n"/>
       <c r="R53" s="24" t="inlineStr">
         <is>
-          <t>Follow-ups-due checkbox; no calendar</t>
+          <t>Grouped overdue, today, this week, later</t>
         </is>
       </c>
       <c r="S53" s="24" t="n"/>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>/school/admissions</t>
+          <t>/school/admissions/follow-ups</t>
         </is>
       </c>
     </row>
@@ -8362,9 +8362,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J57" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J57" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K57" s="33" t="inlineStr">
@@ -8396,7 +8396,7 @@
       <c r="Q57" s="24" t="n"/>
       <c r="R57" s="24" t="inlineStr">
         <is>
-          <t>Verify inside modal; no verification queue</t>
+          <t>One queue across applications, verify or reject with a reason</t>
         </is>
       </c>
       <c r="S57" s="24" t="n"/>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>/school/admissions/applications</t>
+          <t>/school/admissions/verification</t>
         </is>
       </c>
     </row>
@@ -8466,9 +8466,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J58" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J58" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K58" s="33" t="inlineStr">
@@ -8500,7 +8500,7 @@
       <c r="Q58" s="24" t="n"/>
       <c r="R58" s="24" t="inlineStr">
         <is>
-          <t>Scheduling fine; results captured by prompt</t>
+          <t>A form, not a prompt; scheduled kept apart from marked</t>
         </is>
       </c>
       <c r="S58" s="24" t="n"/>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>/school/admissions/applications</t>
+          <t>/school/admissions/assessments</t>
         </is>
       </c>
     </row>
@@ -8570,9 +8570,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J59" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J59" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K59" s="33" t="inlineStr">
@@ -8604,7 +8604,7 @@
       <c r="Q59" s="24" t="n"/>
       <c r="R59" s="24" t="inlineStr">
         <is>
-          <t>Approve and reject are prompt dialogs</t>
+          <t>Approve and reject in a modal with the evidence on screen</t>
         </is>
       </c>
       <c r="S59" s="24" t="n"/>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>/school/admissions/applications</t>
+          <t>/school/admissions/decisions</t>
         </is>
       </c>
     </row>
@@ -9194,9 +9194,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J65" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K65" s="33" t="inlineStr">
@@ -9228,7 +9228,7 @@
       <c r="Q65" s="24" t="n"/>
       <c r="R65" s="24" t="inlineStr">
         <is>
-          <t>Year-by-year enrolment; no subject detail</t>
+          <t>Subjects with teachers, and the years behind</t>
         </is>
       </c>
       <c r="S65" s="24" t="n"/>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>/school/students/[id]</t>
+          <t>/school/students/[id]/academic</t>
         </is>
       </c>
     </row>
@@ -9402,9 +9402,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J67" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K67" s="33" t="inlineStr">
@@ -9436,7 +9436,7 @@
       <c r="Q67" s="24" t="n"/>
       <c r="R67" s="24" t="inlineStr">
         <is>
-          <t>Summary rows; per-paper detail is section-scoped</t>
+          <t>Per paper, with unmarked kept apart from nought</t>
         </is>
       </c>
       <c r="S67" s="24" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>/school/students/[id]</t>
+          <t>/school/students/[id]/exams</t>
         </is>
       </c>
     </row>
@@ -10130,9 +10130,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J74" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -10164,7 +10164,7 @@
       <c r="Q74" s="24" t="n"/>
       <c r="R74" s="24" t="inlineStr">
         <is>
-          <t>Guardians managed; siblings not shown</t>
+          <t>Siblings derived from shared parents, never stored</t>
         </is>
       </c>
       <c r="S74" s="24" t="n"/>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>/school/students/[id]</t>
+          <t>/school/students/[id]/family</t>
         </is>
       </c>
     </row>
@@ -10338,9 +10338,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J76" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J76" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -10372,7 +10372,7 @@
       <c r="Q76" s="24" t="n"/>
       <c r="R76" s="24" t="inlineStr">
         <is>
-          <t>TC and deactivate; no alumni record</t>
+          <t>Derived from enrolment; flags leavers with no certificate</t>
         </is>
       </c>
       <c r="S76" s="24" t="n"/>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>/school/certificates</t>
+          <t>/school/students/leavers</t>
         </is>
       </c>
     </row>
@@ -10650,9 +10650,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J79" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K79" s="33" t="inlineStr">
@@ -10684,7 +10684,7 @@
       <c r="Q79" s="24" t="n"/>
       <c r="R79" s="24" t="inlineStr">
         <is>
-          <t>No parent profile page; name and phone only</t>
+          <t>Profile, linked children, activate and reset</t>
         </is>
       </c>
       <c r="S79" s="24" t="n"/>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>/school/parents</t>
+          <t>/school/parents/[id]</t>
         </is>
       </c>
     </row>
@@ -11170,9 +11170,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J84" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J84" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K84" s="33" t="inlineStr">
@@ -11204,7 +11204,7 @@
       <c r="Q84" s="24" t="n"/>
       <c r="R84" s="24" t="inlineStr">
         <is>
-          <t>Paid and failed list, not per parent</t>
+          <t>Across all their children, not one at a time</t>
         </is>
       </c>
       <c r="S84" s="24" t="n"/>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>/school/fees/online</t>
+          <t>/school/parents/[id]/payments</t>
         </is>
       </c>
     </row>
@@ -11274,14 +11274,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J85" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K85" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J85" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K85" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L85" s="24" t="inlineStr">
@@ -11308,7 +11308,7 @@
       <c r="Q85" s="24" t="n"/>
       <c r="R85" s="24" t="inlineStr">
         <is>
-          <t>Only last login; audit log has no parent filter</t>
+          <t>Audit by actor and by subject, sign-ins stated as unrecorded</t>
         </is>
       </c>
       <c r="S85" s="24" t="n"/>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/parents/[id]/activity</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -5242,9 +5242,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J27" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J27" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K27" s="33" t="inlineStr">
@@ -5276,7 +5276,7 @@
       <c r="Q27" s="24" t="n"/>
       <c r="R27" s="24" t="inlineStr">
         <is>
-          <t>Read-only header; patch endpoint unused</t>
+          <t>Organisation editable via the tenant patch</t>
         </is>
       </c>
       <c r="S27" s="24" t="n"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>/super-admin/tenants/[id]</t>
+          <t>/super-admin/schools</t>
         </is>
       </c>
     </row>
@@ -5346,14 +5346,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J28" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K28" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J28" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L28" s="24" t="inlineStr">
@@ -5380,7 +5380,7 @@
       <c r="Q28" s="24" t="n"/>
       <c r="R28" s="24" t="inlineStr">
         <is>
-          <t>Name and code list only</t>
+          <t>Searchable list with status and contact</t>
         </is>
       </c>
       <c r="S28" s="24" t="n"/>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>/super-admin/tenants/[id]</t>
+          <t>/super-admin/schools</t>
         </is>
       </c>
     </row>
@@ -5866,9 +5866,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J33" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J33" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K33" s="33" t="inlineStr">
@@ -5900,7 +5900,7 @@
       <c r="Q33" s="24" t="n"/>
       <c r="R33" s="24" t="inlineStr">
         <is>
-          <t>Edit form, no branch detail page</t>
+          <t>Branch with its sections and staff</t>
         </is>
       </c>
       <c r="S33" s="24" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>/school/roles</t>
+          <t>/school/branches/[id]</t>
         </is>
       </c>
     </row>
@@ -14602,14 +14602,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J117" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K117" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J117" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K117" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L117" s="24" t="inlineStr">
@@ -14636,7 +14636,7 @@
       <c r="Q117" s="24" t="n"/>
       <c r="R117" s="24" t="inlineStr">
         <is>
-          <t>Attendance keyed by section and date only</t>
+          <t>Lesson marks seeded from the day, never overwriting it</t>
         </is>
       </c>
       <c r="S117" s="24" t="n"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/attendance/periods</t>
         </is>
       </c>
     </row>
@@ -14706,9 +14706,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J118" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J118" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K118" s="33" t="inlineStr">
@@ -14740,7 +14740,7 @@
       <c r="Q118" s="24" t="n"/>
       <c r="R118" s="24" t="inlineStr">
         <is>
-          <t>Matrix is an admin tab; teachers have none</t>
+          <t>Roster grid with the day register showing through</t>
         </is>
       </c>
       <c r="S118" s="24" t="n"/>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>/school/reports/attendance</t>
+          <t>/school/attendance/periods</t>
         </is>
       </c>
     </row>
@@ -14810,14 +14810,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J119" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K119" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J119" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K119" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L119" s="24" t="inlineStr">
@@ -14844,7 +14844,7 @@
       <c r="Q119" s="24" t="n"/>
       <c r="R119" s="24" t="inlineStr">
         <is>
-          <t>Reopen only; no per-student correction request</t>
+          <t>Only an approved request moves the register</t>
         </is>
       </c>
       <c r="S119" s="24" t="n"/>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>/school/attendance-registers</t>
+          <t>/school/attendance/corrections</t>
         </is>
       </c>
     </row>
@@ -15122,14 +15122,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J122" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K122" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J122" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K122" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L122" s="24" t="inlineStr">
@@ -15156,7 +15156,7 @@
       <c r="Q122" s="24" t="n"/>
       <c r="R122" s="24" t="inlineStr">
         <is>
-          <t>Gate passes cover exit, not late entry</t>
+          <t>Late in and early out on the day row, repeat count shown</t>
         </is>
       </c>
       <c r="S122" s="24" t="n"/>
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>/school/front-desk</t>
+          <t>/school/attendance/times</t>
         </is>
       </c>
     </row>
@@ -15226,9 +15226,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J123" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J123" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -15260,7 +15260,7 @@
       <c r="Q123" s="24" t="n"/>
       <c r="R123" s="24" t="inlineStr">
         <is>
-          <t>One tab of three, with CSV</t>
+          <t>Its own page with the CSV</t>
         </is>
       </c>
       <c r="S123" s="24" t="n"/>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>/school/reports/attendance</t>
+          <t>/school/attendance/monthly</t>
         </is>
       </c>
     </row>
@@ -15330,14 +15330,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J124" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K124" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J124" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K124" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L124" s="24" t="inlineStr">
@@ -15364,7 +15364,7 @@
       <c r="Q124" s="24" t="n"/>
       <c r="R124" s="24" t="inlineStr">
         <is>
-          <t>No threshold, at-risk list or contact log</t>
+          <t>At-risk list paired with who has rung home</t>
         </is>
       </c>
       <c r="S124" s="24" t="n"/>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/attendance/at-risk</t>
         </is>
       </c>
     </row>
@@ -24482,14 +24482,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J212" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K212" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J212" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K212" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L212" s="24" t="inlineStr">
@@ -24516,7 +24516,7 @@
       <c r="Q212" s="24" t="n"/>
       <c r="R212" s="24" t="inlineStr">
         <is>
-          <t>A URL field only; no reader or entitlements</t>
+          <t>A catalogue of links, stated as such; no reader exists</t>
         </is>
       </c>
       <c r="S212" s="24" t="n"/>
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>/school/library/catalogue</t>
+          <t>/school/library/digital</t>
         </is>
       </c>
     </row>
@@ -24586,14 +24586,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J213" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K213" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J213" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K213" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L213" s="24" t="inlineStr">
@@ -24620,7 +24620,7 @@
       <c r="Q213" s="24" t="n"/>
       <c r="R213" s="24" t="inlineStr">
         <is>
-          <t>Stat tiles only; no date range or export</t>
+          <t>Date-ranged issues, returns and fines</t>
         </is>
       </c>
       <c r="S213" s="24" t="n"/>
@@ -24652,7 +24652,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>/school/library</t>
+          <t>/school/library/reports</t>
         </is>
       </c>
     </row>
@@ -24898,9 +24898,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J216" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J216" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K216" s="33" t="inlineStr">
@@ -24932,7 +24932,7 @@
       <c r="Q216" s="24" t="n"/>
       <c r="R216" s="24" t="inlineStr">
         <is>
-          <t>Bed by bed only; no allocation register</t>
+          <t>Register with transfer and vacate</t>
         </is>
       </c>
       <c r="S216" s="24" t="n"/>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>/school/hostel</t>
+          <t>/school/hostel/allocations</t>
         </is>
       </c>
     </row>
@@ -25002,9 +25002,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J217" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J217" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K217" s="38" t="inlineStr">
@@ -25036,7 +25036,7 @@
       <c r="Q217" s="24" t="n"/>
       <c r="R217" s="24" t="inlineStr">
         <is>
-          <t>Single warden field, no duty roster</t>
+          <t>Warden per hostel and their open work; no rota model exists</t>
         </is>
       </c>
       <c r="S217" s="24" t="n"/>
@@ -25068,7 +25068,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>/school/hostel</t>
+          <t>/school/hostel/wardens</t>
         </is>
       </c>
     </row>
@@ -26874,14 +26874,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J235" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K235" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J235" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K235" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L235" s="24" t="inlineStr">
@@ -26908,7 +26908,7 @@
       <c r="Q235" s="24" t="n"/>
       <c r="R235" s="24" t="inlineStr">
         <is>
-          <t>Pass number shown, nothing printable</t>
+          <t>Printable pass with a print-only stylesheet</t>
         </is>
       </c>
       <c r="S235" s="24" t="n"/>
@@ -26940,7 +26940,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>/school/front-desk</t>
+          <t>/school/front-desk/passes</t>
         </is>
       </c>
     </row>
@@ -27186,9 +27186,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J238" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J238" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K238" s="38" t="inlineStr">
@@ -27220,7 +27220,7 @@
       <c r="Q238" s="24" t="n"/>
       <c r="R238" s="24" t="inlineStr">
         <is>
-          <t>Vehicle captured; no staff gate log</t>
+          <t>Vehicle gate log; a visit cannot say the arriver is staff</t>
         </is>
       </c>
       <c r="S238" s="24" t="n"/>
@@ -27252,7 +27252,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>/school/front-desk</t>
+          <t>/school/front-desk/staff-log</t>
         </is>
       </c>
     </row>
@@ -27602,14 +27602,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J242" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K242" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J242" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K242" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L242" s="24" t="inlineStr">
@@ -27636,7 +27636,7 @@
       <c r="Q242" s="24" t="n"/>
       <c r="R242" s="24" t="inlineStr">
         <is>
-          <t>One item at a time; no multi-line receipt</t>
+          <t>Multi-line receipt; says lines are recorded individually</t>
         </is>
       </c>
       <c r="S242" s="24" t="n"/>
@@ -27668,7 +27668,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/inventory/receipts</t>
         </is>
       </c>
     </row>
@@ -27706,9 +27706,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J243" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J243" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K243" s="33" t="inlineStr">
@@ -27740,7 +27740,7 @@
       <c r="Q243" s="24" t="n"/>
       <c r="R243" s="24" t="inlineStr">
         <is>
-          <t>Free-text issued-to; no requisition register</t>
+          <t>Issue and return register over free-text issued-to</t>
         </is>
       </c>
       <c r="S243" s="24" t="n"/>
@@ -27772,7 +27772,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/inventory/issues</t>
         </is>
       </c>
     </row>
@@ -28122,9 +28122,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J247" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J247" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K247" s="38" t="inlineStr">
@@ -28156,7 +28156,7 @@
       <c r="Q247" s="24" t="n"/>
       <c r="R247" s="24" t="inlineStr">
         <is>
-          <t>Logs repairs; no schedule or AMC tracking</t>
+          <t>Repair log and warranty; no schedule field exists</t>
         </is>
       </c>
       <c r="S247" s="24" t="n"/>
@@ -28188,7 +28188,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/inventory/maintenance</t>
         </is>
       </c>
     </row>
@@ -28330,14 +28330,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J249" s="38" t="inlineStr">
+      <c r="J249" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K249" s="38" t="inlineStr">
         <is>
           <t>In progress</t>
-        </is>
-      </c>
-      <c r="K249" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
         </is>
       </c>
       <c r="L249" s="24" t="inlineStr">
@@ -28364,7 +28364,7 @@
       <c r="Q249" s="24" t="n"/>
       <c r="R249" s="24" t="inlineStr">
         <is>
-          <t>Equipment is free text; no items or stock</t>
+          <t>Equipment is free text; says so and points at the store</t>
         </is>
       </c>
       <c r="S249" s="24" t="n"/>
@@ -28396,7 +28396,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>/school/facilities</t>
+          <t>/school/inventory/labs</t>
         </is>
       </c>
     </row>
@@ -28538,14 +28538,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J251" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K251" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J251" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K251" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L251" s="24" t="inlineStr">
@@ -28572,7 +28572,7 @@
       <c r="Q251" s="24" t="n"/>
       <c r="R251" s="24" t="inlineStr">
         <is>
-          <t>Tiles and ledger; no date-range report</t>
+          <t>Windowed stock and asset report with charts</t>
         </is>
       </c>
       <c r="S251" s="24" t="n"/>
@@ -28604,7 +28604,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/inventory/reports</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -4514,9 +4514,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J20" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J20" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K20" s="38" t="inlineStr">
@@ -4548,7 +4548,7 @@
       <c r="Q20" s="24" t="n"/>
       <c r="R20" s="24" t="inlineStr">
         <is>
-          <t>Per-tenant cards, no billing screen</t>
+          <t>Subscription, plan and payments; invoicing is not modelled</t>
         </is>
       </c>
       <c r="S20" s="24" t="n"/>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>/super-admin/tenants/[id]</t>
+          <t>/super-admin/billing</t>
         </is>
       </c>
     </row>
@@ -4618,9 +4618,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J21" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J21" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K21" s="33" t="inlineStr">
@@ -4652,7 +4652,7 @@
       <c r="Q21" s="24" t="n"/>
       <c r="R21" s="24" t="inlineStr">
         <is>
-          <t>Usage versus quota card only</t>
+          <t>Usage against quota, per tenant</t>
         </is>
       </c>
       <c r="S21" s="24" t="n"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>/super-admin/tenants/[id]</t>
+          <t>/super-admin/usage</t>
         </is>
       </c>
     </row>
@@ -4722,14 +4722,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J22" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K22" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J22" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K22" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L22" s="24" t="inlineStr">
@@ -4756,7 +4756,7 @@
       <c r="Q22" s="24" t="n"/>
       <c r="R22" s="24" t="inlineStr">
         <is>
-          <t>No platform user management</t>
+          <t>Operator accounts; the last active one cannot be switched off</t>
         </is>
       </c>
       <c r="S22" s="24" t="n"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/super-admin/users</t>
         </is>
       </c>
     </row>
@@ -4826,14 +4826,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J23" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K23" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J23" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K23" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
@@ -4860,7 +4860,7 @@
       <c r="Q23" s="24" t="n"/>
       <c r="R23" s="24" t="inlineStr">
         <is>
-          <t>No ticketing anywhere</t>
+          <t>Internal notes kept out of a non-internal read, in the service</t>
         </is>
       </c>
       <c r="S23" s="24" t="n"/>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/super-admin/tickets</t>
         </is>
       </c>
     </row>
@@ -4930,14 +4930,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J24" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K24" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J24" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L24" s="24" t="inlineStr">
@@ -4964,7 +4964,7 @@
       <c r="Q24" s="24" t="n"/>
       <c r="R24" s="24" t="inlineStr">
         <is>
-          <t>Online pill only, two health endpoints</t>
+          <t>Two things probed; the rest labelled not monitored</t>
         </is>
       </c>
       <c r="S24" s="24" t="n"/>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>/super-admin/health</t>
         </is>
       </c>
     </row>
@@ -5034,14 +5034,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J25" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K25" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J25" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L25" s="24" t="inlineStr">
@@ -5068,7 +5068,7 @@
       <c r="Q25" s="24" t="n"/>
       <c r="R25" s="24" t="inlineStr">
         <is>
-          <t>No global announcements</t>
+          <t>Live only inside its window</t>
         </is>
       </c>
       <c r="S25" s="24" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/super-admin/announcements</t>
         </is>
       </c>
     </row>
@@ -5138,14 +5138,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J26" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K26" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J26" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K26" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L26" s="24" t="inlineStr">
@@ -5172,7 +5172,7 @@
       <c r="Q26" s="24" t="n"/>
       <c r="R26" s="24" t="inlineStr">
         <is>
-          <t>No platform settings screen</t>
+          <t>Known knobs listed before anybody sets them</t>
         </is>
       </c>
       <c r="S26" s="24" t="n"/>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/super-admin/settings</t>
         </is>
       </c>
     </row>
@@ -11586,9 +11586,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J88" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J88" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K88" s="33" t="inlineStr">
@@ -11620,7 +11620,7 @@
       <c r="Q88" s="24" t="n"/>
       <c r="R88" s="24" t="inlineStr">
         <is>
-          <t>No staff profile page, only a row and modal</t>
+          <t>Profile, documents, qualifications and leave in one place</t>
         </is>
       </c>
       <c r="S88" s="24" t="n"/>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>/school/staff</t>
+          <t>/school/staff/[id]</t>
         </is>
       </c>
     </row>
@@ -12002,14 +12002,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J92" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K92" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J92" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K92" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L92" s="24" t="inlineStr">
@@ -12036,7 +12036,7 @@
       <c r="Q92" s="24" t="n"/>
       <c r="R92" s="24" t="inlineStr">
         <is>
-          <t>No workload view anywhere</t>
+          <t>Computed from the timetable; nobody is flagged overloaded</t>
         </is>
       </c>
       <c r="S92" s="24" t="n"/>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/staff/workload</t>
         </is>
       </c>
     </row>
@@ -12106,9 +12106,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J93" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J93" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -12140,7 +12140,7 @@
       <c r="Q93" s="24" t="n"/>
       <c r="R93" s="24" t="inlineStr">
         <is>
-          <t>No qualification fields on the staff record</t>
+          <t>Qualifications with the certificate already on file</t>
         </is>
       </c>
       <c r="S93" s="24" t="n"/>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>/school/documents</t>
+          <t>/school/staff/[id]/qualifications</t>
         </is>
       </c>
     </row>
@@ -12210,9 +12210,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J94" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J94" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K94" s="33" t="inlineStr">
@@ -12244,7 +12244,7 @@
       <c r="Q94" s="24" t="n"/>
       <c r="R94" s="24" t="inlineStr">
         <is>
-          <t>Single day only; no monthly summary</t>
+          <t>A month per person, using the existing analytics</t>
         </is>
       </c>
       <c r="S94" s="24" t="n"/>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>/school/staff-attendance</t>
+          <t>/school/staff/attendance-summary</t>
         </is>
       </c>
     </row>
@@ -12418,14 +12418,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J96" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K96" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J96" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K96" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L96" s="24" t="inlineStr">
@@ -12452,7 +12452,7 @@
       <c r="Q96" s="24" t="n"/>
       <c r="R96" s="24" t="inlineStr">
         <is>
-          <t>No observation or appraisal anywhere</t>
+          <t>What was seen and what to try next; no score field exists</t>
         </is>
       </c>
       <c r="S96" s="24" t="n"/>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/staff/observations</t>
         </is>
       </c>
     </row>
@@ -12522,14 +12522,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J97" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K97" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J97" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K97" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L97" s="24" t="inlineStr">
@@ -12556,7 +12556,7 @@
       <c r="Q97" s="24" t="n"/>
       <c r="R97" s="24" t="inlineStr">
         <is>
-          <t>Deactivate only; no clearance or exit flow</t>
+          <t>Seven areas, none assumed cleared; cannot complete with one open</t>
         </is>
       </c>
       <c r="S97" s="24" t="n"/>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>/school/staff</t>
+          <t>/school/staff/[id]/exit</t>
         </is>
       </c>
     </row>
@@ -21362,14 +21362,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J182" s="38" t="inlineStr">
+      <c r="J182" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K182" s="38" t="inlineStr">
         <is>
           <t>In progress</t>
-        </is>
-      </c>
-      <c r="K182" s="33" t="inlineStr">
-        <is>
-          <t>Done</t>
         </is>
       </c>
       <c r="L182" s="24" t="inlineStr">
@@ -21396,7 +21396,7 @@
       <c r="Q182" s="24" t="n"/>
       <c r="R182" s="24" t="inlineStr">
         <is>
-          <t>Per application; no interview calendar</t>
+          <t>Week view with clashes; wants a list-interviews endpoint</t>
         </is>
       </c>
       <c r="S182" s="24" t="n"/>
@@ -21428,7 +21428,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>/school/recruitment</t>
+          <t>/school/recruitment/interviews</t>
         </is>
       </c>
     </row>
@@ -25834,14 +25834,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J225" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K225" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J225" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K225" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L225" s="24" t="inlineStr">
@@ -25868,7 +25868,7 @@
       <c r="Q225" s="24" t="n"/>
       <c r="R225" s="24" t="inlineStr">
         <is>
-          <t>One medicine field; no register or stock</t>
+          <t>Append-only; a correction supersedes rather than edits</t>
         </is>
       </c>
       <c r="S225" s="24" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>/school/health</t>
+          <t>/school/health/medication</t>
         </is>
       </c>
     </row>
@@ -25938,9 +25938,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J226" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J226" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K226" s="33" t="inlineStr">
@@ -25972,7 +25972,7 @@
       <c r="Q226" s="24" t="n"/>
       <c r="R226" s="24" t="inlineStr">
         <is>
-          <t>Split across tabs; no drive or bulk entry</t>
+          <t>Bulk entry for a drive, capped per section</t>
         </is>
       </c>
       <c r="S226" s="24" t="n"/>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>/school/health</t>
+          <t>/school/health/immunisation</t>
         </is>
       </c>
     </row>
@@ -26042,14 +26042,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J227" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K227" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J227" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K227" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L227" s="24" t="inlineStr">
@@ -26076,7 +26076,7 @@
       <c r="Q227" s="24" t="n"/>
       <c r="R227" s="24" t="inlineStr">
         <is>
-          <t>Next-session date only; no booking diary</t>
+          <t>Private notes never selected, not filtered later</t>
         </is>
       </c>
       <c r="S227" s="24" t="n"/>
@@ -26108,7 +26108,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>/school/counselling</t>
+          <t>/school/counselling/diary</t>
         </is>
       </c>
     </row>
@@ -26354,9 +26354,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J230" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J230" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K230" s="33" t="inlineStr">
@@ -26388,7 +26388,7 @@
       <c r="Q230" s="24" t="n"/>
       <c r="R230" s="24" t="inlineStr">
         <is>
-          <t>No way to mark an action served</t>
+          <t>A sanction can be marked served, and outstanding ones show</t>
         </is>
       </c>
       <c r="S230" s="24" t="n"/>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>/school/discipline</t>
+          <t>/school/discipline/actions</t>
         </is>
       </c>
     </row>
@@ -26458,14 +26458,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J231" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K231" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J231" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K231" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L231" s="24" t="inlineStr">
@@ -26492,7 +26492,7 @@
       <c r="Q231" s="24" t="n"/>
       <c r="R231" s="24" t="inlineStr">
         <is>
-          <t>Contacts shown; no escalation chain</t>
+          <t>Ordered chain that renumbers when one is removed</t>
         </is>
       </c>
       <c r="S231" s="24" t="n"/>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>/school/health</t>
+          <t>/school/health/emergency</t>
         </is>
       </c>
     </row>
@@ -32490,9 +32490,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J289" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J289" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K289" s="33" t="inlineStr">
@@ -32524,7 +32524,7 @@
       <c r="Q289" s="24" t="n"/>
       <c r="R289" s="24" t="inlineStr">
         <is>
-          <t>Sources, columns, run and export; no filter UI</t>
+          <t>Filter keys the source actually accepts, no invented operators</t>
         </is>
       </c>
       <c r="S289" s="24" t="n"/>
@@ -32556,7 +32556,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>/school/data-desk</t>
+          <t>/school/data-desk/reports/[id]</t>
         </is>
       </c>
     </row>
@@ -32906,9 +32906,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J293" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J293" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K293" s="33" t="inlineStr">
@@ -32940,7 +32940,7 @@
       <c r="Q293" s="24" t="n"/>
       <c r="R293" s="24" t="inlineStr">
         <is>
-          <t>Per-role grid, no cross-role matrix</t>
+          <t>Cross-role grid, editable, with a differences-only view</t>
         </is>
       </c>
       <c r="S293" s="24" t="n"/>
@@ -32972,7 +32972,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>/school/roles</t>
+          <t>/school/roles/matrix</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -15538,14 +15538,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J126" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K126" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K126" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L126" s="24" t="inlineStr">
@@ -15572,7 +15572,7 @@
       <c r="Q126" s="24" t="n"/>
       <c r="R126" s="24" t="inlineStr">
         <is>
-          <t>Only a clashes panel, no dashboard stats</t>
+          <t>How complete every week is, and who clashes</t>
         </is>
       </c>
       <c r="S126" s="24" t="n"/>
@@ -15642,14 +15642,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J127" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K127" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J127" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K127" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L127" s="24" t="inlineStr">
@@ -15676,7 +15676,7 @@
       <c r="Q127" s="24" t="n"/>
       <c r="R127" s="24" t="inlineStr">
         <is>
-          <t>Grid assigns subject; entries carry no room</t>
+          <t>The week, with a room against a slot</t>
         </is>
       </c>
       <c r="S127" s="24" t="n"/>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>/school/timetable</t>
+          <t>/school/timetable/setup</t>
         </is>
       </c>
     </row>
@@ -15850,14 +15850,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J129" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K129" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J129" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K129" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L129" s="24" t="inlineStr">
@@ -15884,7 +15884,7 @@
       <c r="Q129" s="24" t="n"/>
       <c r="R129" s="24" t="inlineStr">
         <is>
-          <t>Date-range blocks, not a weekly grid</t>
+          <t>Weekly grid over the recurring blocks</t>
         </is>
       </c>
       <c r="S129" s="24" t="n"/>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>/school/cover</t>
+          <t>/school/timetable/availability</t>
         </is>
       </c>
     </row>
@@ -15954,14 +15954,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J130" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K130" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J130" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K130" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L130" s="24" t="inlineStr">
@@ -15988,7 +15988,7 @@
       <c r="Q130" s="24" t="n"/>
       <c r="R130" s="24" t="inlineStr">
         <is>
-          <t>No generator; manual entry and copy only</t>
+          <t>Places what fits and names what it could not</t>
         </is>
       </c>
       <c r="S130" s="24" t="n"/>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/timetable/generate</t>
         </is>
       </c>
     </row>
@@ -16162,14 +16162,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J132" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K132" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J132" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K132" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L132" s="24" t="inlineStr">
@@ -16196,7 +16196,7 @@
       <c r="Q132" s="24" t="n"/>
       <c r="R132" s="24" t="inlineStr">
         <is>
-          <t>Own week only; no coordinator view</t>
+          <t>One day across every section</t>
         </is>
       </c>
       <c r="S132" s="24" t="n"/>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>/teacher/timetable</t>
+          <t>/school/timetable/coordinator</t>
         </is>
       </c>
     </row>
@@ -19074,9 +19074,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J160" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J160" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K160" s="33" t="inlineStr">
@@ -19108,7 +19108,7 @@
       <c r="Q160" s="24" t="n"/>
       <c r="R160" s="24" t="inlineStr">
         <is>
-          <t>Accountant dashboard is a placeholder</t>
+          <t>Collected against owed, with the month trend</t>
         </is>
       </c>
       <c r="S160" s="24" t="n"/>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>/accountant</t>
+          <t>/school/fees/dashboard</t>
         </is>
       </c>
     </row>
@@ -19386,14 +19386,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J163" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K163" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J163" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K163" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L163" s="24" t="inlineStr">
@@ -19420,7 +19420,7 @@
       <c r="Q163" s="24" t="n"/>
       <c r="R163" s="24" t="inlineStr">
         <is>
-          <t>No per-student fee plan; class structures only</t>
+          <t>Names an absolute amount or adds a head; concessions still subtract</t>
         </is>
       </c>
       <c r="S163" s="24" t="n"/>
@@ -19452,7 +19452,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/fees/assignments</t>
         </is>
       </c>
     </row>
@@ -19802,14 +19802,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J167" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K167" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J167" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K167" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L167" s="24" t="inlineStr">
@@ -19836,7 +19836,7 @@
       <c r="Q167" s="24" t="n"/>
       <c r="R167" s="24" t="inlineStr">
         <is>
-          <t>No staff-side per-student ledger</t>
+          <t>Derived running balance, fees and receipts in date order</t>
         </is>
       </c>
       <c r="S167" s="24" t="n"/>
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>/parent/children/[id]/fees</t>
+          <t>/school/fees/ledger/[studentId]</t>
         </is>
       </c>
     </row>
@@ -19906,14 +19906,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J168" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K168" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J168" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K168" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L168" s="24" t="inlineStr">
@@ -19940,7 +19940,7 @@
       <c r="Q168" s="24" t="n"/>
       <c r="R168" s="24" t="inlineStr">
         <is>
-          <t>A filter, not a dues or ageing report</t>
+          <t>Ageing buckets with the reminder run</t>
         </is>
       </c>
       <c r="S168" s="24" t="n"/>
@@ -19972,7 +19972,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>/school/fees</t>
+          <t>/school/fees/dues</t>
         </is>
       </c>
     </row>
@@ -20530,9 +20530,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J174" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J174" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K174" s="33" t="inlineStr">
@@ -20564,7 +20564,7 @@
       <c r="Q174" s="24" t="n"/>
       <c r="R174" s="24" t="inlineStr">
         <is>
-          <t>Supplier master; no ledger or payables</t>
+          <t>Payables derived from bills minus payments</t>
         </is>
       </c>
       <c r="S174" s="24" t="n"/>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/purchasing/vendors</t>
         </is>
       </c>
     </row>
@@ -20634,14 +20634,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J175" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K175" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J175" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K175" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L175" s="24" t="inlineStr">
@@ -20668,7 +20668,7 @@
       <c r="Q175" s="24" t="n"/>
       <c r="R175" s="24" t="inlineStr">
         <is>
-          <t>No purchase order, bill or payment tracking</t>
+          <t>Orders, bills and payments; a bill cannot be overpaid</t>
         </is>
       </c>
       <c r="S175" s="24" t="n"/>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>/school/inventory</t>
+          <t>/school/purchasing/orders</t>
         </is>
       </c>
     </row>
@@ -20842,14 +20842,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J177" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K177" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J177" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K177" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L177" s="24" t="inlineStr">
@@ -20876,7 +20876,7 @@
       <c r="Q177" s="24" t="n"/>
       <c r="R177" s="24" t="inlineStr">
         <is>
-          <t>CSV and builder; no finance report pack</t>
+          <t>Income against expenditure over a window</t>
         </is>
       </c>
       <c r="S177" s="24" t="n"/>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>/school/exports</t>
+          <t>/school/accounts/reports</t>
         </is>
       </c>
     </row>
@@ -28850,14 +28850,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J254" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K254" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J254" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K254" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L254" s="24" t="inlineStr">
@@ -28884,7 +28884,7 @@
       <c r="Q254" s="24" t="n"/>
       <c r="R254" s="24" t="inlineStr">
         <is>
-          <t>Consent roster only; no attendance</t>
+          <t>Attendance kept apart from consent; unticked is not absent</t>
         </is>
       </c>
       <c r="S254" s="24" t="n"/>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>/school/events</t>
+          <t>/school/events/[id]</t>
         </is>
       </c>
     </row>
@@ -29058,14 +29058,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J256" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K256" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J256" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K256" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L256" s="24" t="inlineStr">
@@ -29092,7 +29092,7 @@
       <c r="Q256" s="24" t="n"/>
       <c r="R256" s="24" t="inlineStr">
         <is>
-          <t>Admin-only setup; teachers cannot create</t>
+          <t>A teacher arranges for their own class only</t>
         </is>
       </c>
       <c r="S256" s="24" t="n"/>
@@ -29124,7 +29124,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>/school/ptm</t>
+          <t>/teacher/ptm</t>
         </is>
       </c>
     </row>
@@ -29370,9 +29370,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J259" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J259" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K259" s="38" t="inlineStr">
@@ -29404,7 +29404,7 @@
       <c r="Q259" s="24" t="n"/>
       <c r="R259" s="24" t="inlineStr">
         <is>
-          <t>Teacher and parent only; admin has no inbox</t>
+          <t>Who is talking, not what they said; no admin participant exists</t>
         </is>
       </c>
       <c r="S259" s="24" t="n"/>
@@ -29436,7 +29436,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>/teacher/messages</t>
+          <t>/school/messages</t>
         </is>
       </c>
     </row>
@@ -29474,9 +29474,9 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J260" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J260" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="K260" s="38" t="inlineStr">
@@ -29508,7 +29508,7 @@
       <c r="Q260" s="24" t="n"/>
       <c r="R260" s="24" t="inlineStr">
         <is>
-          <t>SMS and email skipped; schedule not wired</t>
+          <t>Scheduling recorded; no scheduler runs it</t>
         </is>
       </c>
       <c r="S260" s="24" t="n"/>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>/school/notices</t>
+          <t>/school/notices/campaigns</t>
         </is>
       </c>
     </row>
@@ -29578,14 +29578,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J261" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K261" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J261" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K261" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L261" s="24" t="inlineStr">
@@ -29612,7 +29612,7 @@
       <c r="Q261" s="24" t="n"/>
       <c r="R261" s="24" t="inlineStr">
         <is>
-          <t>Per-notice delivery only, no history log</t>
+          <t>Delivery across notices, skipped kept apart from failed</t>
         </is>
       </c>
       <c r="S261" s="24" t="n"/>
@@ -29644,7 +29644,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>/school/notices</t>
+          <t>/school/notices/history</t>
         </is>
       </c>
     </row>
@@ -33842,14 +33842,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J302" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K302" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J302" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K302" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L302" s="24" t="inlineStr">
@@ -33876,7 +33876,7 @@
       <c r="Q302" s="24" t="n"/>
       <c r="R302" s="24" t="inlineStr">
         <is>
-          <t>Parents only; staff have no inbox page</t>
+          <t>That person own post, with unread falling when read</t>
         </is>
       </c>
       <c r="S302" s="24" t="n"/>
@@ -33908,7 +33908,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>/parent/notices</t>
+          <t>/staff/inbox</t>
         </is>
       </c>
     </row>

--- a/School_ERP_296_Development_Tracker.xlsx
+++ b/School_ERP_296_Development_Tracker.xlsx
@@ -3678,14 +3678,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J12" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K12" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J12" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L12" s="24" t="inlineStr">
@@ -3712,7 +3712,7 @@
       <c r="Q12" s="24" t="n"/>
       <c r="R12" s="24" t="inlineStr">
         <is>
-          <t>Parent login says OTP coming soon</t>
+          <t>Two-step when the school requires it; no tokens without the code</t>
         </is>
       </c>
       <c r="S12" s="24" t="n"/>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/parent/login</t>
         </is>
       </c>
     </row>
@@ -10858,14 +10858,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J81" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K81" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K81" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L81" s="24" t="inlineStr">
@@ -10892,7 +10892,7 @@
       <c r="Q81" s="24" t="n"/>
       <c r="R81" s="24" t="inlineStr">
         <is>
-          <t>No notification preference UI or model</t>
+          <t>Opt-out, and attendance and fees cannot be silenced</t>
         </is>
       </c>
       <c r="S81" s="24" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/parent/preferences</t>
         </is>
       </c>
     </row>
@@ -13146,14 +13146,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J103" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K103" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J103" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K103" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L103" s="24" t="inlineStr">
@@ -13180,7 +13180,7 @@
       <c r="Q103" s="24" t="n"/>
       <c r="R103" s="24" t="inlineStr">
         <is>
-          <t>No subject-group entity anywhere</t>
+          <t>Groups of subjects, electives marked</t>
         </is>
       </c>
       <c r="S103" s="24" t="n"/>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/subjects/groups</t>
         </is>
       </c>
     </row>
@@ -13250,14 +13250,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J104" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="K104" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="J104" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K104" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L104" s="24" t="inlineStr">
@@ -13284,7 +13284,7 @@
       <c r="Q104" s="24" t="n"/>
       <c r="R104" s="24" t="inlineStr">
         <is>
-          <t>No curriculum entity with board and status</t>
+          <t>One active per class and year; activating retires the last</t>
         </is>
       </c>
       <c r="S104" s="24" t="n"/>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>/school/syllabus</t>
+          <t>/school/curriculum</t>
         </is>
       </c>
     </row>
@@ -14394,14 +14394,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J115" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K115" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J115" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K115" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L115" s="24" t="inlineStr">
@@ -14428,7 +14428,7 @@
       <c r="Q115" s="24" t="n"/>
       <c r="R115" s="24" t="inlineStr">
         <is>
-          <t>No activity or club register</t>
+          <t>Clubs and teams with a roll and a capacity</t>
         </is>
       </c>
       <c r="S115" s="24" t="n"/>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/activities</t>
         </is>
       </c>
     </row>
@@ -20946,14 +20946,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J178" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K178" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J178" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K178" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L178" s="24" t="inlineStr">
@@ -20980,7 +20980,7 @@
       <c r="Q178" s="24" t="n"/>
       <c r="R178" s="24" t="inlineStr">
         <is>
-          <t>No requisition or approval to hire</t>
+          <t>Cannot be approved by whoever raised it</t>
         </is>
       </c>
       <c r="S178" s="24" t="n"/>
@@ -21012,7 +21012,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/recruitment/requisitions</t>
         </is>
       </c>
     </row>
@@ -21367,9 +21367,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="K182" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="K182" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L182" s="24" t="inlineStr">
@@ -21396,7 +21396,7 @@
       <c r="Q182" s="24" t="n"/>
       <c r="R182" s="24" t="inlineStr">
         <is>
-          <t>Week view with clashes; wants a list-interviews endpoint</t>
+          <t>Now one query for a window, not eighty</t>
         </is>
       </c>
       <c r="S182" s="24" t="n"/>
@@ -21570,14 +21570,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J184" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K184" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J184" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K184" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L184" s="24" t="inlineStr">
@@ -21604,7 +21604,7 @@
       <c r="Q184" s="24" t="n"/>
       <c r="R184" s="24" t="inlineStr">
         <is>
-          <t>No onboarding checklist anywhere</t>
+          <t>Standard tasks laid out, none assumed done</t>
         </is>
       </c>
       <c r="S184" s="24" t="n"/>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/staff/onboarding</t>
         </is>
       </c>
     </row>
@@ -25007,9 +25007,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="K217" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="K217" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L217" s="24" t="inlineStr">
@@ -25036,7 +25036,7 @@
       <c r="Q217" s="24" t="n"/>
       <c r="R217" s="24" t="inlineStr">
         <is>
-          <t>Warden per hostel and their open work; no rota model exists</t>
+          <t>A rota that names the nights nobody covers</t>
         </is>
       </c>
       <c r="S217" s="24" t="n"/>
@@ -28127,9 +28127,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="K247" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="K247" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L247" s="24" t="inlineStr">
@@ -28156,7 +28156,7 @@
       <c r="Q247" s="24" t="n"/>
       <c r="R247" s="24" t="inlineStr">
         <is>
-          <t>Repair log and warranty; no schedule field exists</t>
+          <t>Service interval; no interval means not due, not overdue</t>
         </is>
       </c>
       <c r="S247" s="24" t="n"/>
@@ -29479,9 +29479,9 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="K260" s="38" t="inlineStr">
-        <is>
-          <t>In progress</t>
+      <c r="K260" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L260" s="24" t="inlineStr">
@@ -29508,7 +29508,7 @@
       <c r="Q260" s="24" t="n"/>
       <c r="R260" s="24" t="inlineStr">
         <is>
-          <t>Scheduling recorded; no scheduler runs it</t>
+          <t>A run command a cron or a button can call</t>
         </is>
       </c>
       <c r="S260" s="24" t="n"/>
@@ -33322,14 +33322,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J297" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K297" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J297" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K297" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L297" s="24" t="inlineStr">
@@ -33356,7 +33356,7 @@
       <c r="Q297" s="24" t="n"/>
       <c r="R297" s="24" t="inlineStr">
         <is>
-          <t>No notification channel or template settings</t>
+          <t>Channels and templates, with categories that carry meaning</t>
         </is>
       </c>
       <c r="S297" s="24" t="n"/>
@@ -33388,7 +33388,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/settings/notifications</t>
         </is>
       </c>
     </row>
@@ -33530,14 +33530,14 @@
           <t>Ready</t>
         </is>
       </c>
-      <c r="J299" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="K299" s="39" t="inlineStr">
-        <is>
-          <t>Not started</t>
+      <c r="J299" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K299" s="33" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="L299" s="24" t="inlineStr">
@@ -33564,7 +33564,7 @@
       <c r="Q299" s="24" t="n"/>
       <c r="R299" s="24" t="inlineStr">
         <is>
-          <t>No password policy anywhere</t>
+          <t>Policy enforced on change and reset, not just displayed</t>
         </is>
       </c>
       <c r="S299" s="24" t="n"/>
@@ -33596,7 +33596,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/school/settings/security</t>
         </is>
       </c>
     </row>
